--- a/KeywordDrivenTest/_TestData/CreateCaseFromIncidents/TestCase_2_CreateCaseFromIncidents.xlsx
+++ b/KeywordDrivenTest/_TestData/CreateCaseFromIncidents/TestCase_2_CreateCaseFromIncidents.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28605"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="219" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34FA092B-F5BE-41F4-B7A3-667E5300420F}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C47EBB21-59C4-4F11-85A0-9439C0D30D31}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="53">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Step2</t>
   </si>
   <si>
-    <t>IncidentCaseNumber</t>
+    <t>DetectiveCaseNumber</t>
   </si>
   <si>
     <t>linkCase00001</t>
@@ -750,6 +750,9 @@
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
@@ -813,6 +816,9 @@
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
       <c r="B15" t="s">
         <v>40</v>
       </c>
@@ -876,6 +882,9 @@
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
       <c r="B19" t="s">
         <v>45</v>
       </c>
@@ -939,6 +948,9 @@
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
       <c r="B23" t="s">
         <v>50</v>
       </c>
